--- a/Config/Datas/OptionDatas/Options.xlsx
+++ b/Config/Datas/OptionDatas/Options.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\OptionDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EBF677-802E-40AC-AEBD-BF03FCD01F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D33FDC-D46E-42FF-882A-99FC416ECEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,14 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CGA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>list,Condition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +120,18 @@
   </si>
   <si>
     <t>砍价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得声望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,CGA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -493,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
@@ -504,6 +508,7 @@
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -517,13 +522,13 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -555,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -577,14 +582,14 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -600,14 +605,14 @@
         <v>3</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -620,19 +625,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -641,50 +646,58 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N7">
         <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/OptionDatas/Options.xlsx
+++ b/Config/Datas/OptionDatas/Options.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\OptionDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D33FDC-D46E-42FF-882A-99FC416ECEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE303EF-4F63-4AE6-B0EC-C7594EF22A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/OptionDatas/Options.xlsx
+++ b/Config/Datas/OptionDatas/Options.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\OptionDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE303EF-4F63-4AE6-B0EC-C7594EF22A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA90163-8CED-4CF6-97B5-C3BAFF9B3157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,6 +132,89 @@
   </si>
   <si>
     <t>list,CGA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_移动_向上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_移动_向下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_移动_向左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_移动_向右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌选项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使食材向左移动1格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使食材向上移动1格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使食材向下移动1格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使食材向右移动1格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_方向位移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,DV_值~1,棋盘上</t>
+  </si>
+  <si>
+    <t>左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
@@ -700,6 +783,118 @@
         <v>20</v>
       </c>
     </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" t="s">
+        <v>44</v>
+      </c>
+      <c r="O24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>41</v>
+      </c>
+      <c r="M25" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" t="s">
+        <v>45</v>
+      </c>
+      <c r="O25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" t="s">
+        <v>42</v>
+      </c>
+      <c r="N26" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>41</v>
+      </c>
+      <c r="M27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" t="s">
+        <v>46</v>
+      </c>
+      <c r="O27" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="F1:Q1"/>

--- a/Config/Datas/OptionDatas/Options.xlsx
+++ b/Config/Datas/OptionDatas/Options.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\OptionDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA90163-8CED-4CF6-97B5-C3BAFF9B3157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DBD178-114F-49BC-BA06-4F2DAB881887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -580,21 +580,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="31.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.58203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.58203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +626,7 @@
       <c r="Q1" s="6"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -657,7 +657,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -680,7 +680,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -703,7 +703,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -735,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -761,7 +761,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L8" t="s">
         <v>24</v>
       </c>
@@ -769,7 +769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -783,7 +783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -791,7 +791,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>27</v>
       </c>
@@ -817,7 +817,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>28</v>
       </c>
@@ -843,7 +843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>29</v>
       </c>
@@ -869,7 +869,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -893,6 +893,11 @@
       </c>
       <c r="O27" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/OptionDatas/Options.xlsx
+++ b/Config/Datas/OptionDatas/Options.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\OptionDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DBD178-114F-49BC-BA06-4F2DAB881887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD7EAAC-5B40-4AD4-9513-CBBA577065DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -581,20 +581,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S31"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.58203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="31.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.58203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +626,7 @@
       <c r="Q1" s="6"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -657,7 +657,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -680,7 +680,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -703,7 +703,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -735,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -761,7 +761,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="L8" t="s">
         <v>24</v>
       </c>
@@ -769,7 +769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -783,7 +783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -791,7 +791,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>27</v>
       </c>
@@ -817,7 +817,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>28</v>
       </c>
@@ -843,7 +843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>29</v>
       </c>
@@ -869,7 +869,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
